--- a/2026/YRIGOYEN 7630/Mayo/YRIGOYEN7630-Mayo.xlsx
+++ b/2026/YRIGOYEN 7630/Mayo/YRIGOYEN7630-Mayo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA4978-8B9C-4CB5-808B-FDBD19D13A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD68E0C-4907-49B4-AE2D-201A2F5C1E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$115</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -299,9 +304,6 @@
     <t>Federacion patronal  Seguro obligatorio de consorcio</t>
   </si>
   <si>
-    <t>Subidos en En3r0</t>
-  </si>
-  <si>
     <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE YRIGOYEN 7630</t>
   </si>
   <si>
@@ -332,42 +334,15 @@
     <t>Facundo comandatore</t>
   </si>
   <si>
-    <t>Debito 06/04</t>
-  </si>
-  <si>
     <t>SERVICIOS DE MANTENIMIENTO</t>
   </si>
   <si>
-    <t>Debito 10/04</t>
-  </si>
-  <si>
-    <t>Matafuegos MEGASEG - Recarga anual de matafuegos</t>
-  </si>
-  <si>
-    <t>Transf 10/04</t>
-  </si>
-  <si>
-    <t>Debito 13/04</t>
-  </si>
-  <si>
-    <t>Debito 16/04</t>
-  </si>
-  <si>
-    <t>Trans 26/04</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Limpieza de 4 columnas pluviales y colectora de pluvial a la calle</t>
-  </si>
-  <si>
     <t>cristina - Joatan Fernandez</t>
   </si>
   <si>
     <t>Ivan Gstavo Almeyda</t>
   </si>
   <si>
-    <t>Departamento 3 - Cuota 1 de reintegro de materiales de arreglos de pisos</t>
-  </si>
-  <si>
     <t>VTO 18/06</t>
   </si>
   <si>
@@ -377,31 +352,15 @@
     <t>Gustavo padron - Sr contador honorarios MAYO</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se adeuda MAYO</t>
-  </si>
-  <si>
     <t>Sindicatos mes de MAYO</t>
   </si>
   <si>
-    <t>Se informa que el inquilino de la unidad funcional N.º 15 se mudó en el mes de diciembre de 2025 a la unidad funcional N.º 14, dentro del mismo edificio. Debido a la falta de notificación oportuna a la administración sobre dicho cambio, se produjo un error en la imputación de pagos en las expensas correspondientes a los meses de enero, febrero y abril de 2026, los cuales fueron asignados a la unidad funcional N.º 15 cuando en realidad correspondían a la unidad funcional N.º 14.
-En consecuencia, en la presente liquidación de expensas se procede a regularizar dicha situación, corrigiendo la imputación de los pagos entre ambas unidades funcionales.</t>
-  </si>
-  <si>
-    <t>Pagos imputados en abril de 2026 a Unidad funcional incorrecta</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Limpieza de columna cocina y baño de todas las UF - Cuota 2/5</t>
-  </si>
-  <si>
     <t>Transf 22/05</t>
   </si>
   <si>
     <t>Transf 21/05</t>
   </si>
   <si>
-    <t>Julio Doartero - 3er cuota obra piso dpto. 3</t>
-  </si>
-  <si>
     <t>Transf 08/05</t>
   </si>
   <si>
@@ -409,6 +368,27 @@
   </si>
   <si>
     <t>Trans 12/05</t>
+  </si>
+  <si>
+    <t>Transf 05/05</t>
+  </si>
+  <si>
+    <t>Debito 11/05</t>
+  </si>
+  <si>
+    <t>Debito 18/05</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Abril y Mayo</t>
+  </si>
+  <si>
+    <t>Subidos en Juni0 a 165000</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Limpieza de columna cocina y baño de todas las UF - Cuota 3/5</t>
+  </si>
+  <si>
+    <t>Transf 26/05</t>
   </si>
 </sst>
 </file>
@@ -622,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,12 +669,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1107,7 +1081,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1336,9 +1310,6 @@
     <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="16" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1372,17 +1343,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="25" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1390,95 +1373,51 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1557,9 +1496,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1597,9 +1536,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1632,9 +1571,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1667,9 +1623,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1843,22 +1816,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M119"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="69" t="s">
         <v>54</v>
@@ -1867,7 +1840,7 @@
       <c r="D1" s="69"/>
       <c r="E1" s="70"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="71" t="s">
         <v>28</v>
@@ -1876,16 +1849,16 @@
       <c r="D2" s="71"/>
       <c r="E2" s="72"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="202" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="203"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="187" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="188"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1896,12 +1869,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="71" t="s">
@@ -1909,68 +1882,68 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="205" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="205"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="205"/>
-      <c r="C10" s="205"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="204" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="190" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="190"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="204"/>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="204"/>
-      <c r="B15" s="204"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="204"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="204"/>
-      <c r="B16" s="204"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="204"/>
-      <c r="E16" s="204"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="189"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="189"/>
+      <c r="B14" s="189"/>
+      <c r="C14" s="189"/>
+      <c r="D14" s="189"/>
+      <c r="E14" s="189"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="189"/>
+      <c r="B15" s="189"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="189"/>
+      <c r="B16" s="189"/>
+      <c r="C16" s="189"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1979,7 +1952,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>34</v>
       </c>
@@ -1988,245 +1961,246 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="170">
-        <v>963103</v>
+      <c r="D22" s="169">
+        <v>972126</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="170"/>
+      <c r="D23" s="169"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="57"/>
       <c r="C24" s="57"/>
-      <c r="D24" s="171">
+      <c r="D24" s="170">
         <f>SUM(D22:D23)</f>
-        <v>963103</v>
+        <v>972126</v>
       </c>
       <c r="E24" s="139"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="170"/>
+      <c r="D25" s="169"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="170">
+      <c r="D26" s="169">
         <v>0</v>
       </c>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="170">
+      <c r="D27" s="169">
         <v>0</v>
       </c>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="172"/>
+      <c r="D28" s="171"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="57" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="57"/>
       <c r="C29" s="57"/>
-      <c r="D29" s="173">
+      <c r="D29" s="172">
         <f>SUM(D25:D28)</f>
         <v>0</v>
       </c>
       <c r="E29" s="139"/>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
-      <c r="D30" s="174"/>
+      <c r="D30" s="173"/>
       <c r="E30" s="140">
         <f>D24+D29</f>
-        <v>963103</v>
+        <v>972126</v>
       </c>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B31" s="35"/>
       <c r="C31" s="35"/>
-      <c r="D31" s="175"/>
+      <c r="D31" s="174"/>
       <c r="E31" s="141"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="194" t="s">
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="185" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="186"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="169">
+        <v>45000</v>
+      </c>
+      <c r="E32" s="142"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="195"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="170">
-        <v>45000</v>
-      </c>
-      <c r="E32" s="142"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="194" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="195"/>
+      <c r="B33" s="186"/>
       <c r="C33" s="52"/>
-      <c r="D33" s="176">
-        <v>0</v>
+      <c r="D33" s="175">
+        <f>147300*2</f>
+        <v>294600</v>
       </c>
       <c r="E33" s="142"/>
       <c r="H33" s="152" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
-      <c r="D34" s="177"/>
+      <c r="D34" s="176"/>
       <c r="E34" s="143">
         <f>SUM(D32:D33)</f>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>339600</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
-      <c r="D35" s="178"/>
+      <c r="D35" s="177"/>
       <c r="E35" s="144"/>
     </row>
-    <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="192" t="s">
+    <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="191" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="193"/>
+      <c r="B36" s="192"/>
       <c r="C36" s="54"/>
-      <c r="D36" s="179">
+      <c r="D36" s="178">
         <f>26570+7909</f>
         <v>34479</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="194" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="185" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="195"/>
+      <c r="B37" s="186"/>
       <c r="C37" s="54"/>
-      <c r="D37" s="180">
+      <c r="D37" s="179">
         <v>54278</v>
       </c>
       <c r="E37" s="145" t="str">
         <f>E36</f>
-        <v>Debito 06/04</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 11/05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="177"/>
+      <c r="D38" s="176"/>
       <c r="E38" s="146">
         <f>SUM(D36:D37)</f>
         <v>88757</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="147"/>
       <c r="C39" s="147"/>
-      <c r="D39" s="181"/>
+      <c r="D39" s="180"/>
       <c r="E39" s="148"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="52"/>
-      <c r="D40" s="222">
+      <c r="D40" s="181">
         <v>681424.8</v>
       </c>
-      <c r="E40" s="154" t="s">
-        <v>103</v>
+      <c r="E40" s="163" t="s">
+        <v>113</v>
       </c>
       <c r="G40" s="124"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="52"/>
-      <c r="D41" s="182">
+      <c r="D41" s="181">
         <v>10602.27</v>
       </c>
       <c r="E41" s="154" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="52"/>
-      <c r="D42" s="182">
+      <c r="D42" s="181">
         <v>75532.289999999994</v>
       </c>
       <c r="E42" s="154" t="str">
         <f>E41</f>
-        <v>Debito 16/04</v>
+        <v>Debito 18/05</v>
       </c>
       <c r="F42" s="43">
         <f>D42+D41</f>
@@ -2234,90 +2208,91 @@
       </c>
       <c r="G42" s="138"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="221">
+      <c r="D43" s="157">
         <v>102476.36</v>
       </c>
-      <c r="E43" s="154" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E43" s="154" t="str">
+        <f>E42</f>
+        <v>Debito 18/05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de MAYO</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="221">
+      <c r="D44" s="157">
         <v>6219.95</v>
       </c>
       <c r="E44" s="155" t="str">
         <f>E43</f>
-        <v>Debito 13/04</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>Debito 18/05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de MAYO</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="221">
+      <c r="D45" s="157">
         <v>55979.55</v>
       </c>
       <c r="E45" s="156" t="str">
         <f>E44</f>
-        <v>Debito 13/04</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 18/05</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
         <v>3</v>
       </c>
       <c r="B46" s="147"/>
       <c r="C46" s="147"/>
-      <c r="D46" s="183"/>
+      <c r="D46" s="182"/>
       <c r="E46" s="146">
         <f>SUM(D40:D45)</f>
         <v>932235.22000000009</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="35" t="s">
         <v>18</v>
       </c>
       <c r="B47" s="147"/>
       <c r="C47" s="147"/>
-      <c r="D47" s="181"/>
+      <c r="D47" s="180"/>
       <c r="E47" s="148"/>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B48" s="157"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="221">
+      <c r="D48" s="157">
         <v>82654.19</v>
       </c>
       <c r="E48" s="154" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B49" s="157"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="221">
+      <c r="D49" s="157">
         <v>35559.360000000001</v>
       </c>
       <c r="E49" s="154" t="str">
@@ -2325,13 +2300,13 @@
         <v>Transf 08/05</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="221">
+      <c r="D50" s="157">
         <v>29818.65</v>
       </c>
       <c r="E50" s="154" t="str">
@@ -2339,654 +2314,576 @@
         <v>Transf 08/05</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="192" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="193"/>
+      <c r="B51" s="192"/>
       <c r="C51" s="5"/>
       <c r="D51" s="157">
-        <v>0</v>
-      </c>
-      <c r="E51" s="154"/>
-    </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>838862.61</v>
+      </c>
+      <c r="E51" s="154" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
-      <c r="D52" s="184"/>
+      <c r="D52" s="183"/>
       <c r="E52" s="146">
         <f>SUM(D48:D51)</f>
-        <v>148032.20000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>986894.81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="177"/>
+      <c r="D53" s="176"/>
       <c r="E53" s="149"/>
     </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="159" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B54" s="153"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="221">
+      <c r="D54" s="157">
         <v>93200</v>
       </c>
       <c r="E54" s="158" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" s="153"/>
       <c r="C55" s="5"/>
       <c r="D55" s="157">
-        <v>0</v>
-      </c>
-      <c r="E55" s="158"/>
-    </row>
-    <row r="56" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="192" t="s">
-        <v>120</v>
-      </c>
-      <c r="B56" s="193"/>
+        <v>55000</v>
+      </c>
+      <c r="E55" s="158" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="191" t="s">
+        <v>117</v>
+      </c>
+      <c r="B56" s="192"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="128">
+      <c r="D56" s="106">
         <v>333100</v>
       </c>
       <c r="E56" s="158" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="192" t="s">
-        <v>109</v>
-      </c>
-      <c r="B57" s="193"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="191" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="192"/>
       <c r="C57" s="5"/>
       <c r="D57" s="106">
-        <v>221300</v>
+        <v>250000</v>
       </c>
       <c r="E57" s="158" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="192" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="193"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="191" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" s="192"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="128">
-        <v>250000</v>
+      <c r="D58" s="106">
+        <v>78200</v>
       </c>
       <c r="E58" s="158" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="159" t="s">
-        <v>123</v>
-      </c>
-      <c r="B59" s="153"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="128">
-        <v>600000</v>
-      </c>
-      <c r="E59" s="164" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="192" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="193"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="106">
-        <v>162000</v>
-      </c>
-      <c r="E60" s="164" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="192" t="s">
-        <v>112</v>
-      </c>
-      <c r="B61" s="193"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="150">
+        <f>SUM(D54:D58)</f>
+        <v>809500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="67"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="173"/>
+      <c r="E60" s="149"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="106">
-        <v>126700</v>
-      </c>
-      <c r="E61" s="164"/>
-    </row>
-    <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="192" t="s">
-        <v>94</v>
-      </c>
-      <c r="B62" s="193"/>
+      <c r="D61" s="157">
+        <v>58300</v>
+      </c>
+      <c r="E61" s="151"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="106"/>
-      <c r="E62" s="158"/>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="29" t="s">
+      <c r="D62" s="157">
+        <v>81498.02</v>
+      </c>
+      <c r="E62" s="40"/>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" s="51"/>
+      <c r="C63" s="51"/>
+      <c r="D63" s="109"/>
+      <c r="E63" s="103">
+        <f>SUM(D61:D62)</f>
+        <v>139798.02000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="102"/>
+      <c r="E64" s="110"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="111"/>
+      <c r="E65" s="112"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="D66" s="113"/>
+      <c r="E66" s="114"/>
+      <c r="F66" s="43"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="115"/>
+      <c r="E67" s="116">
+        <f>(SUM(E27:E65))</f>
+        <v>4268911.0500000007</v>
+      </c>
+      <c r="F67" s="138"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="124"/>
+      <c r="I67" s="124"/>
+      <c r="J67" s="124"/>
+      <c r="K67" s="124"/>
+      <c r="L67" s="124"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D68" s="113"/>
+      <c r="E68" s="113"/>
+      <c r="H68" s="124"/>
+      <c r="I68" s="124"/>
+      <c r="J68" s="124"/>
+      <c r="K68" s="124"/>
+      <c r="L68" s="124"/>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="113"/>
+      <c r="E69" s="113"/>
+      <c r="H69" s="162"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" s="12"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="117"/>
+      <c r="E70" s="118"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="191"/>
+      <c r="B71" s="192"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="128"/>
+      <c r="E71" s="104"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="191"/>
+      <c r="B72" s="192"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="106"/>
+      <c r="E72" s="104"/>
+    </row>
+    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="185"/>
+      <c r="B73" s="186"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="106"/>
+      <c r="E73" s="104"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="105"/>
+      <c r="B74" s="107"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="106"/>
+      <c r="E74" s="104"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="49"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="58">
+        <f>SUM(D71:D74)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="101"/>
+    </row>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" s="10"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="68">
+        <f>E75+E78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="100">
+        <f>E67</f>
+        <v>4268911.0500000007</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" s="100">
+        <f>E67-E65</f>
+        <v>4268911.0500000007</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="100">
+        <f>E80-E78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="100">
+        <f>E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D87" s="124"/>
+      <c r="E87" s="124"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D88" s="124"/>
+      <c r="E88" s="124"/>
+    </row>
+    <row r="89" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B89" s="125"/>
+      <c r="C89" s="24"/>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="33"/>
+      <c r="B90" s="59">
+        <v>0</v>
+      </c>
+      <c r="C90" s="26"/>
+    </row>
+    <row r="91" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="40">
+        <f>PRORRATEO!F29</f>
+        <v>3645653.3100000005</v>
+      </c>
+      <c r="C91" s="24"/>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="40">
+        <v>0</v>
+      </c>
+      <c r="C92" s="24"/>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" s="108">
+        <f>B114</f>
+        <v>0</v>
+      </c>
+      <c r="C93" s="24"/>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="28"/>
+      <c r="B94" s="47"/>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="123" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95" s="47"/>
+      <c r="C95" s="24"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B96" s="47">
+        <f>-B83</f>
+        <v>-4268911.0500000007</v>
+      </c>
+      <c r="C96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" s="47">
+        <f>-(B84)</f>
+        <v>0</v>
+      </c>
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="150">
-        <f>SUM(D54:D62)</f>
-        <v>1786300</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="67"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="174"/>
-      <c r="E64" s="149"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="157">
-        <v>58300</v>
-      </c>
-      <c r="E65" s="151"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="157">
-        <v>52317.84</v>
-      </c>
-      <c r="E66" s="40"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="109"/>
-      <c r="E67" s="103">
-        <f>SUM(D65:D66)</f>
-        <v>110617.84</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="102"/>
-      <c r="E68" s="110"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="111"/>
-      <c r="E69" s="112"/>
-    </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1"/>
-      <c r="D70" s="113"/>
-      <c r="E70" s="114"/>
-      <c r="F70" s="43"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="115"/>
-      <c r="E71" s="116">
-        <f>(SUM(E27:E69))</f>
-        <v>4074045.2600000002</v>
-      </c>
-      <c r="F71" s="138"/>
-      <c r="G71" s="43"/>
-      <c r="H71" s="124"/>
-      <c r="I71" s="124"/>
-      <c r="J71" s="124"/>
-      <c r="K71" s="124"/>
-      <c r="L71" s="124"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D72" s="113"/>
-      <c r="E72" s="113"/>
-      <c r="H72" s="124"/>
-      <c r="I72" s="124"/>
-      <c r="J72" s="124"/>
-      <c r="K72" s="124"/>
-      <c r="L72" s="124"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D73" s="113"/>
-      <c r="E73" s="113"/>
-      <c r="H73" s="162"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="117"/>
-      <c r="E74" s="118"/>
-    </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="192"/>
-      <c r="B75" s="193"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="128"/>
-      <c r="E75" s="104"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="192"/>
-      <c r="B76" s="193"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="106"/>
-      <c r="E76" s="104"/>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="194"/>
-      <c r="B77" s="195"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="106"/>
-      <c r="E77" s="104"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="105"/>
-      <c r="B78" s="107"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="106"/>
-      <c r="E78" s="104"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="49"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58">
-        <f>SUM(D75:D78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="101"/>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B84" s="10"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="68">
-        <f>E79+E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="100">
-        <f>E71</f>
-        <v>4074045.2600000002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" s="100">
-        <f>E71-E69</f>
-        <v>4074045.2600000002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="100">
-        <f>E84-E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" s="100">
-        <f>E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D91" s="124"/>
-      <c r="E91" s="124"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="196" t="s">
-        <v>118</v>
-      </c>
-      <c r="B92" s="197"/>
-      <c r="C92" s="188"/>
-      <c r="D92" s="189"/>
-      <c r="E92" s="189"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="198"/>
-      <c r="B93" s="199"/>
-      <c r="C93" s="188"/>
-      <c r="D93" s="189"/>
-      <c r="E93" s="189"/>
-    </row>
-    <row r="94" spans="1:5" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="200"/>
-      <c r="B94" s="201"/>
-      <c r="C94" s="188"/>
-      <c r="D94" s="189"/>
-      <c r="E94" s="189"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D95" s="124"/>
-      <c r="E95" s="124"/>
-    </row>
-    <row r="96" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B96" s="125"/>
-      <c r="C96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="33"/>
-      <c r="B97" s="59">
-        <v>0</v>
-      </c>
-      <c r="C97" s="26"/>
-    </row>
-    <row r="98" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B98" s="40">
+      <c r="B98" s="59">
+        <f>SUM(B90:B97)</f>
+        <v>-623257.74000000022</v>
+      </c>
+      <c r="C98" s="27"/>
+      <c r="D98" s="43"/>
+    </row>
+    <row r="99" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="41"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="43"/>
+      <c r="E99" s="126"/>
+      <c r="F99" s="127"/>
+    </row>
+    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="42"/>
+      <c r="C100" s="27"/>
+    </row>
+    <row r="101" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101"/>
+      <c r="B101" s="41"/>
+      <c r="C101" s="37"/>
+    </row>
+    <row r="102" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="B102" s="184">
+        <v>-1101016.7960999962</v>
+      </c>
+      <c r="C102" s="37"/>
+      <c r="D102" s="46"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B103" s="136">
+        <f>-B83</f>
+        <v>-4268911.0500000007</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B104" s="136">
+        <f>-B84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="136">
+        <f>B114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B106" s="137">
         <f>PRORRATEO!F29</f>
-        <v>4401284.3499999996</v>
-      </c>
-      <c r="C98" s="24"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="25"/>
-      <c r="B99" s="40">
-        <v>0</v>
-      </c>
-      <c r="C99" s="24"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B100" s="108">
-        <f>B122</f>
-        <v>0</v>
-      </c>
-      <c r="C100" s="24"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="28"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="B102" s="47"/>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B103" s="47">
-        <f>-B87</f>
-        <v>-4074045.2600000002</v>
-      </c>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B104" s="47">
-        <f>-(B88)</f>
-        <v>0</v>
-      </c>
-      <c r="C104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="32" t="s">
+        <v>3645653.3100000005</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="134" t="s">
+        <v>48</v>
+      </c>
+      <c r="B107" s="135">
+        <f>SUM(B102:C106)</f>
+        <v>-1724274.5360999964</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="132"/>
+      <c r="B108" s="132"/>
+    </row>
+    <row r="109" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="194" t="s">
+        <v>32</v>
+      </c>
+      <c r="B110" s="194"/>
+      <c r="C110" s="194"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="194"/>
+      <c r="B111" s="194"/>
+      <c r="C111" s="194"/>
+    </row>
+    <row r="112" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="120"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="36">
+        <v>40000</v>
+      </c>
+      <c r="E112" s="138"/>
+    </row>
+    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="120"/>
+      <c r="B113" s="122"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="138"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="59">
-        <f>SUM(B97:B104)</f>
-        <v>327239.08999999939</v>
-      </c>
-      <c r="C105" s="27"/>
-      <c r="D105" s="43"/>
-    </row>
-    <row r="106" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="41"/>
-      <c r="C106" s="27"/>
-      <c r="D106" s="43"/>
-      <c r="E106" s="126"/>
-      <c r="F106" s="127"/>
-    </row>
-    <row r="107" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="42"/>
-      <c r="C107" s="27"/>
-    </row>
-    <row r="108" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108"/>
-      <c r="B108" s="41"/>
-      <c r="C108" s="37"/>
-    </row>
-    <row r="109" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="131" t="s">
-        <v>85</v>
-      </c>
-      <c r="B109" s="185">
-        <v>-1107166.1660999954</v>
-      </c>
-      <c r="C109" s="37"/>
-      <c r="D109" s="46"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B110" s="136">
-        <f>-B87</f>
-        <v>-4074045.2600000002</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="B111" s="136">
-        <f>-B88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="186" t="s">
-        <v>119</v>
-      </c>
-      <c r="B112" s="187">
-        <f>-124551-124551*2</f>
-        <v>-373653</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="B113" s="136">
-        <f>B122</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="B114" s="137">
-        <f>PRORRATEO!F29</f>
-        <v>4401284.3499999996</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="134" t="s">
-        <v>48</v>
-      </c>
-      <c r="B115" s="135">
-        <f>SUM(B109:C114)</f>
-        <v>-1153580.0760999955</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="132"/>
-      <c r="B116" s="132"/>
-    </row>
-    <row r="117" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="191" t="s">
-        <v>32</v>
-      </c>
-      <c r="B118" s="191"/>
-      <c r="C118" s="191"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="191"/>
-      <c r="B119" s="191"/>
-      <c r="C119" s="191"/>
-    </row>
-    <row r="120" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="120"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="36">
-        <v>40000</v>
-      </c>
-      <c r="E120" s="138"/>
-    </row>
-    <row r="121" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="120"/>
-      <c r="B121" s="122"/>
-      <c r="C121" s="119"/>
-      <c r="D121" s="138"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B122" s="121">
-        <f>SUM(B120:B121)</f>
-        <v>0</v>
-      </c>
-      <c r="C122" s="45"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M123" s="8"/>
-    </row>
-    <row r="124" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="190"/>
-      <c r="B124" s="190"/>
-      <c r="C124" s="190"/>
-      <c r="D124" s="190"/>
-      <c r="E124" s="190"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125" s="190"/>
-      <c r="B125" s="190"/>
-      <c r="C125" s="190"/>
-      <c r="D125" s="190"/>
-      <c r="E125" s="190"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126" s="190"/>
-      <c r="B126" s="190"/>
-      <c r="C126" s="190"/>
-      <c r="D126" s="190"/>
-      <c r="E126" s="190"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A127" s="190"/>
-      <c r="B127" s="190"/>
-      <c r="C127" s="190"/>
-      <c r="D127" s="190"/>
-      <c r="E127" s="190"/>
+      <c r="B114" s="121">
+        <f>SUM(B112:B113)</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="45"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="8"/>
+    </row>
+    <row r="116" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="193"/>
+      <c r="B116" s="193"/>
+      <c r="C116" s="193"/>
+      <c r="D116" s="193"/>
+      <c r="E116" s="193"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="193"/>
+      <c r="B117" s="193"/>
+      <c r="C117" s="193"/>
+      <c r="D117" s="193"/>
+      <c r="E117" s="193"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="193"/>
+      <c r="B118" s="193"/>
+      <c r="C118" s="193"/>
+      <c r="D118" s="193"/>
+      <c r="E118" s="193"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="193"/>
+      <c r="B119" s="193"/>
+      <c r="C119" s="193"/>
+      <c r="D119" s="193"/>
+      <c r="E119" s="193"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="16">
+    <mergeCell ref="A116:E119"/>
+    <mergeCell ref="A110:C111"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A124:E127"/>
-    <mergeCell ref="A118:C119"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A92:B94"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2997,44 +2894,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
     <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="0.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="0.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3053,13 +2950,14 @@
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="130">
-        <v>3962982.6285000001</v>
+        <f>3962982.6285+(3962982.6285*5%)</f>
+        <v>4161131.7599250004</v>
       </c>
       <c r="M2" s="55"/>
       <c r="N2" s="55"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3075,73 +2973,73 @@
       <c r="M3" s="56"/>
       <c r="N3" s="60"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="206" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="198" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="206" t="s">
+      <c r="F4" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="216" t="s">
+      <c r="G4" s="204" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="198" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="198" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="219" t="s">
+      <c r="K4" s="207" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="214" t="s">
+      <c r="M4" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="209" t="s">
+      <c r="N4" s="195" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="130">
         <v>3774269.17</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="208"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="213"/>
-      <c r="K5" s="220"/>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="203"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="208"/>
       <c r="L5" s="61" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="M5" s="215"/>
-      <c r="N5" s="210"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="201"/>
+      <c r="N5" s="196"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="64">
         <v>1</v>
       </c>
@@ -3153,11 +3051,11 @@
         <v>6.69</v>
       </c>
       <c r="E6" s="74">
-        <v>258261.01</v>
+        <v>270886.01</v>
       </c>
       <c r="F6" s="75">
         <f t="shared" ref="F6" si="0">E6</f>
-        <v>258261.01</v>
+        <v>270886.01</v>
       </c>
       <c r="G6" s="76">
         <f t="shared" ref="G6:G23" si="1">E6-F6</f>
@@ -3172,7 +3070,7 @@
       </c>
       <c r="J6" s="78">
         <f>L$2*D6/100</f>
-        <v>265123.53784665006</v>
+        <v>278379.71473898255</v>
       </c>
       <c r="K6" s="161">
         <f t="shared" ref="K6:K23" si="2">F$2*D6/100</f>
@@ -3180,21 +3078,21 @@
       </c>
       <c r="L6" s="80">
         <f>ROUND(SUM(G6:K6),0) + O6</f>
-        <v>270886.01</v>
+        <v>284142.01</v>
       </c>
       <c r="M6" s="81">
         <f>ROUND(L6*6% + L6,0) + O6</f>
-        <v>287139.01</v>
+        <v>301191.01</v>
       </c>
       <c r="N6" s="82">
         <f>ROUND(L6*3%,0) + L6</f>
-        <v>279013.01</v>
+        <v>292666.01</v>
       </c>
       <c r="O6" s="43">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64">
         <f>A6+1</f>
         <v>2</v>
@@ -3207,23 +3105,23 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="74">
-        <v>1359637.02</v>
+        <v>1638514.02</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="76">
         <f t="shared" si="1"/>
-        <v>1359637.02</v>
+        <v>1638514.02</v>
       </c>
       <c r="H7" s="76">
         <f t="shared" ref="H7:H23" si="3">IF(G7&gt;0,G7*3%,0)</f>
-        <v>40789.1106</v>
+        <v>49155.420599999998</v>
       </c>
       <c r="I7" s="77">
         <v>0</v>
       </c>
       <c r="J7" s="78">
         <f t="shared" ref="J7:J23" si="4">L$2*D7%</f>
-        <v>233023.37855580001</v>
+        <v>244674.54748359002</v>
       </c>
       <c r="K7" s="161">
         <f t="shared" si="2"/>
@@ -3231,15 +3129,15 @@
       </c>
       <c r="L7" s="80">
         <f t="shared" ref="L7:L23" si="5">ROUND(SUM(G7:K7),0) + O7</f>
-        <v>1638514.02</v>
+        <v>1937409.02</v>
       </c>
       <c r="M7" s="81">
         <f t="shared" ref="M7:M23" si="6">ROUND(L7*6% + L7,0) + O7</f>
-        <v>1736825.02</v>
+        <v>2053654.02</v>
       </c>
       <c r="N7" s="82">
         <f t="shared" ref="N7:N23" si="7">ROUND(L7*3%,0) + L7</f>
-        <v>1687669.02</v>
+        <v>1995531.02</v>
       </c>
       <c r="O7" s="43">
         <f>O6+0.01</f>
@@ -3247,28 +3145,28 @@
       </c>
       <c r="P7" s="43"/>
     </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="165">
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="164">
         <f t="shared" ref="A8:A23" si="8">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="165" t="s">
+      <c r="B8" s="164" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="166"/>
-      <c r="D8" s="167">
+      <c r="C8" s="165"/>
+      <c r="D8" s="166">
         <v>6.65</v>
       </c>
       <c r="E8" s="75">
-        <v>256717.03</v>
+        <v>142566.03</v>
       </c>
       <c r="F8" s="75">
-        <f>E8+RESUMEN!D61</f>
-        <v>383417.03</v>
+        <f>E8+4</f>
+        <v>142570.03</v>
       </c>
       <c r="G8" s="76">
         <f t="shared" si="1"/>
-        <v>-126700.00000000003</v>
+        <v>-4</v>
       </c>
       <c r="H8" s="76">
         <f t="shared" si="3"/>
@@ -3279,7 +3177,7 @@
       </c>
       <c r="J8" s="78">
         <f t="shared" si="4"/>
-        <v>263538.34479525004</v>
+        <v>276715.26203501254</v>
       </c>
       <c r="K8" s="161">
         <f t="shared" si="2"/>
@@ -3287,22 +3185,22 @@
       </c>
       <c r="L8" s="80">
         <f t="shared" si="5"/>
-        <v>142566.03</v>
+        <v>282439.03000000003</v>
       </c>
       <c r="M8" s="81">
         <f t="shared" si="6"/>
-        <v>151120.03</v>
+        <v>299385.03000000003</v>
       </c>
       <c r="N8" s="82">
         <f t="shared" si="7"/>
-        <v>146843.03</v>
+        <v>290912.03000000003</v>
       </c>
       <c r="O8" s="43">
         <f t="shared" ref="O8:O24" si="9">O7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="64">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -3315,11 +3213,11 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="74">
-        <v>259805.04</v>
+        <v>272506.03999999998</v>
       </c>
       <c r="F9" s="75">
         <f t="shared" ref="F9:F23" si="10">E9</f>
-        <v>259805.04</v>
+        <v>272506.03999999998</v>
       </c>
       <c r="G9" s="76">
         <f t="shared" si="1"/>
@@ -3334,7 +3232,7 @@
       </c>
       <c r="J9" s="78">
         <f t="shared" si="4"/>
-        <v>266708.73089805001</v>
+        <v>280044.16744295252</v>
       </c>
       <c r="K9" s="161">
         <f t="shared" si="2"/>
@@ -3342,15 +3240,15 @@
       </c>
       <c r="L9" s="80">
         <f t="shared" si="5"/>
-        <v>272506.03999999998</v>
+        <v>285841.03999999998</v>
       </c>
       <c r="M9" s="81">
         <f t="shared" si="6"/>
-        <v>288856.03999999998</v>
+        <v>302992.03999999998</v>
       </c>
       <c r="N9" s="82">
         <f t="shared" si="7"/>
-        <v>280681.03999999998</v>
+        <v>294416.03999999998</v>
       </c>
       <c r="O9" s="43">
         <f t="shared" si="9"/>
@@ -3358,7 +3256,7 @@
       </c>
       <c r="Q9" s="43"/>
     </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="64">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -3371,26 +3269,25 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="74">
-        <v>886499.05</v>
+        <v>325601.05</v>
       </c>
       <c r="F10" s="75">
-        <f>E10-50</f>
-        <v>886449.05</v>
+        <v>191523.06</v>
       </c>
       <c r="G10" s="76">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>134077.99</v>
       </c>
       <c r="H10" s="76">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>4022.3396999999995</v>
       </c>
       <c r="I10" s="77">
         <v>0</v>
       </c>
       <c r="J10" s="78">
         <f t="shared" si="4"/>
-        <v>318623.80333139998</v>
+        <v>334554.99349796999</v>
       </c>
       <c r="K10" s="161">
         <f t="shared" si="2"/>
@@ -3398,26 +3295,26 @@
       </c>
       <c r="L10" s="80">
         <f t="shared" si="5"/>
-        <v>325601.05</v>
+        <v>479581.05</v>
       </c>
       <c r="M10" s="81">
         <f t="shared" si="6"/>
-        <v>345137.05</v>
+        <v>508356.05</v>
       </c>
       <c r="N10" s="82">
         <f t="shared" si="7"/>
-        <v>335369.05</v>
+        <v>493968.05</v>
       </c>
       <c r="O10" s="43">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
       <c r="P10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q10" s="43"/>
     </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="64">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -3430,15 +3327,14 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="74">
-        <v>182597.06</v>
+        <v>197269.06</v>
       </c>
       <c r="F11" s="75">
-        <f t="shared" si="10"/>
-        <v>182597.06</v>
+        <v>335369.05</v>
       </c>
       <c r="G11" s="76">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-138099.99</v>
       </c>
       <c r="H11" s="76">
         <f t="shared" si="3"/>
@@ -3449,7 +3345,7 @@
       </c>
       <c r="J11" s="78">
         <f t="shared" si="4"/>
-        <v>187449.07832805</v>
+        <v>196821.53224445254</v>
       </c>
       <c r="K11" s="161">
         <f t="shared" si="2"/>
@@ -3457,27 +3353,27 @@
       </c>
       <c r="L11" s="80">
         <f t="shared" si="5"/>
-        <v>191523.06</v>
+        <v>62796.06</v>
       </c>
       <c r="M11" s="81">
         <f t="shared" si="6"/>
-        <v>203014.06</v>
+        <v>66564.06</v>
       </c>
       <c r="N11" s="82">
         <f t="shared" si="7"/>
-        <v>197269.06</v>
+        <v>64680.06</v>
       </c>
       <c r="O11" s="43">
         <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="165">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="164">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="B12" s="165" t="s">
+      <c r="B12" s="164" t="s">
         <v>62</v>
       </c>
       <c r="C12" s="64"/>
@@ -3485,23 +3381,23 @@
         <v>5.67</v>
       </c>
       <c r="E12" s="74">
-        <v>485736.07</v>
+        <v>729893.07</v>
       </c>
       <c r="F12" s="75"/>
       <c r="G12" s="76">
         <f t="shared" si="1"/>
-        <v>485736.07</v>
+        <v>729893.07</v>
       </c>
       <c r="H12" s="76">
         <f t="shared" si="3"/>
-        <v>14572.0821</v>
+        <v>21896.792099999999</v>
       </c>
       <c r="I12" s="77">
         <v>0</v>
       </c>
       <c r="J12" s="78">
         <f t="shared" si="4"/>
-        <v>224701.11503595</v>
+        <v>235936.17078774751</v>
       </c>
       <c r="K12" s="161">
         <f t="shared" si="2"/>
@@ -3509,22 +3405,22 @@
       </c>
       <c r="L12" s="80">
         <f t="shared" si="5"/>
-        <v>729893.07</v>
+        <v>992610.07</v>
       </c>
       <c r="M12" s="81">
         <f t="shared" si="6"/>
-        <v>773687.07</v>
+        <v>1052167.07</v>
       </c>
       <c r="N12" s="82">
         <f t="shared" si="7"/>
-        <v>751790.07</v>
+        <v>1022388.07</v>
       </c>
       <c r="O12" s="43">
         <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64">
         <f t="shared" si="8"/>
         <v>8</v>
@@ -3537,15 +3433,15 @@
         <v>5.67</v>
       </c>
       <c r="E13" s="74">
-        <v>218885.08</v>
+        <v>236472.08</v>
       </c>
       <c r="F13" s="75">
-        <f>E13+1</f>
-        <v>218886.08</v>
+        <f>E13</f>
+        <v>236472.08</v>
       </c>
       <c r="G13" s="76">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="76">
         <f t="shared" si="3"/>
@@ -3556,7 +3452,7 @@
       </c>
       <c r="J13" s="78">
         <f t="shared" si="4"/>
-        <v>224701.11503595</v>
+        <v>235936.17078774751</v>
       </c>
       <c r="K13" s="161">
         <f t="shared" si="2"/>
@@ -3564,15 +3460,15 @@
       </c>
       <c r="L13" s="80">
         <f t="shared" si="5"/>
-        <v>229584.08</v>
+        <v>240820.08</v>
       </c>
       <c r="M13" s="81">
         <f t="shared" si="6"/>
-        <v>243359.08</v>
+        <v>255269.08</v>
       </c>
       <c r="N13" s="82">
         <f t="shared" si="7"/>
-        <v>236472.08</v>
+        <v>248045.08</v>
       </c>
       <c r="O13" s="43">
         <f t="shared" si="9"/>
@@ -3582,7 +3478,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64">
         <f t="shared" si="8"/>
         <v>9</v>
@@ -3595,11 +3491,11 @@
         <v>7.67</v>
       </c>
       <c r="E14" s="74">
-        <v>296093.09000000003</v>
+        <v>310567.09000000003</v>
       </c>
       <c r="F14" s="75">
         <f t="shared" si="10"/>
-        <v>296093.09000000003</v>
+        <v>310567.09000000003</v>
       </c>
       <c r="G14" s="76">
         <f t="shared" si="1"/>
@@ -3614,7 +3510,7 @@
       </c>
       <c r="J14" s="78">
         <f t="shared" si="4"/>
-        <v>303960.76760595001</v>
+        <v>319158.80598624755</v>
       </c>
       <c r="K14" s="161">
         <f t="shared" si="2"/>
@@ -3622,22 +3518,22 @@
       </c>
       <c r="L14" s="80">
         <f t="shared" si="5"/>
-        <v>310567.09000000003</v>
+        <v>325765.09000000003</v>
       </c>
       <c r="M14" s="81">
         <f t="shared" si="6"/>
-        <v>329201.09000000003</v>
+        <v>345311.09</v>
       </c>
       <c r="N14" s="82">
         <f t="shared" si="7"/>
-        <v>319884.09000000003</v>
+        <v>335538.09000000003</v>
       </c>
       <c r="O14" s="43">
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -3650,12 +3546,15 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="74">
-        <v>-143359.9</v>
-      </c>
-      <c r="F15" s="75"/>
+        <v>55047.1</v>
+      </c>
+      <c r="F15" s="75">
+        <f>E15</f>
+        <v>55047.1</v>
+      </c>
       <c r="G15" s="76">
         <f t="shared" si="1"/>
-        <v>-143359.9</v>
+        <v>0</v>
       </c>
       <c r="H15" s="76">
         <f t="shared" si="3"/>
@@ -3666,7 +3565,7 @@
       </c>
       <c r="J15" s="78">
         <f t="shared" si="4"/>
-        <v>194186.14879650003</v>
+        <v>203895.45623632503</v>
       </c>
       <c r="K15" s="161">
         <f t="shared" si="2"/>
@@ -3674,22 +3573,22 @@
       </c>
       <c r="L15" s="80">
         <f t="shared" si="5"/>
-        <v>55047.1</v>
+        <v>208116.1</v>
       </c>
       <c r="M15" s="81">
         <f t="shared" si="6"/>
-        <v>58350.1</v>
+        <v>220603.1</v>
       </c>
       <c r="N15" s="82">
         <f t="shared" si="7"/>
-        <v>56698.1</v>
+        <v>214359.1</v>
       </c>
       <c r="O15" s="43">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -3702,11 +3601,11 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="74">
-        <v>217341.11</v>
+        <v>227965.11</v>
       </c>
       <c r="F16" s="75">
         <f t="shared" si="10"/>
-        <v>217341.11</v>
+        <v>227965.11</v>
       </c>
       <c r="G16" s="76">
         <f t="shared" si="1"/>
@@ -3721,7 +3620,7 @@
       </c>
       <c r="J16" s="78">
         <f t="shared" si="4"/>
-        <v>223115.92198454999</v>
+        <v>234271.71808377749</v>
       </c>
       <c r="K16" s="161">
         <f t="shared" si="2"/>
@@ -3729,22 +3628,22 @@
       </c>
       <c r="L16" s="80">
         <f t="shared" si="5"/>
-        <v>227965.11</v>
+        <v>239121.11</v>
       </c>
       <c r="M16" s="81">
         <f t="shared" si="6"/>
-        <v>241643.11</v>
+        <v>253468.11</v>
       </c>
       <c r="N16" s="82">
         <f t="shared" si="7"/>
-        <v>234804.11</v>
+        <v>246295.11</v>
       </c>
       <c r="O16" s="43">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64">
         <f t="shared" si="8"/>
         <v>12</v>
@@ -3757,11 +3656,11 @@
         <v>5.55</v>
       </c>
       <c r="E17" s="74">
-        <v>214252.12</v>
+        <v>224726.12</v>
       </c>
       <c r="F17" s="75">
         <f t="shared" si="10"/>
-        <v>214252.12</v>
+        <v>224726.12</v>
       </c>
       <c r="G17" s="76">
         <f t="shared" si="1"/>
@@ -3776,7 +3675,7 @@
       </c>
       <c r="J17" s="78">
         <f t="shared" si="4"/>
-        <v>219945.53588174999</v>
+        <v>230942.81267583751</v>
       </c>
       <c r="K17" s="161">
         <f t="shared" si="2"/>
@@ -3784,22 +3683,22 @@
       </c>
       <c r="L17" s="80">
         <f t="shared" si="5"/>
-        <v>224726.12</v>
+        <v>235723.12</v>
       </c>
       <c r="M17" s="81">
         <f t="shared" si="6"/>
-        <v>238210.12</v>
+        <v>249867.12</v>
       </c>
       <c r="N17" s="82">
         <f t="shared" si="7"/>
-        <v>231468.12</v>
+        <v>242795.12</v>
       </c>
       <c r="O17" s="43">
         <f t="shared" si="9"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -3812,11 +3711,11 @@
         <v>11.06</v>
       </c>
       <c r="E18" s="74">
-        <v>426961.13</v>
+        <v>447832.13</v>
       </c>
       <c r="F18" s="75">
         <f t="shared" si="10"/>
-        <v>426961.13</v>
+        <v>447832.13</v>
       </c>
       <c r="G18" s="76">
         <f t="shared" si="1"/>
@@ -3831,7 +3730,7 @@
       </c>
       <c r="J18" s="78">
         <f t="shared" si="4"/>
-        <v>438305.87871210004</v>
+        <v>460221.17264770507</v>
       </c>
       <c r="K18" s="161">
         <f t="shared" si="2"/>
@@ -3839,22 +3738,22 @@
       </c>
       <c r="L18" s="80">
         <f t="shared" si="5"/>
-        <v>447832.13</v>
+        <v>469748.13</v>
       </c>
       <c r="M18" s="81">
         <f t="shared" si="6"/>
-        <v>474702.13</v>
+        <v>497933.13</v>
       </c>
       <c r="N18" s="82">
         <f t="shared" si="7"/>
-        <v>461267.13</v>
+        <v>483840.13</v>
       </c>
       <c r="O18" s="43">
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -3867,26 +3766,26 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="74">
-        <v>771047.14</v>
+        <v>208649.14</v>
       </c>
       <c r="F19" s="75">
-        <f>124551+200000.14+124551+124551+124551</f>
-        <v>698204.14</v>
+        <f>130778+72843</f>
+        <v>203621</v>
       </c>
       <c r="G19" s="76">
         <f t="shared" si="1"/>
-        <v>72843</v>
+        <v>5028.140000000014</v>
       </c>
       <c r="H19" s="76">
         <f t="shared" si="3"/>
-        <v>2185.29</v>
+        <v>150.84420000000043</v>
       </c>
       <c r="I19" s="77">
         <v>0</v>
       </c>
       <c r="J19" s="78">
         <f t="shared" si="4"/>
-        <v>130778.42674050001</v>
+        <v>137317.34807752501</v>
       </c>
       <c r="K19" s="161">
         <f t="shared" si="2"/>
@@ -3894,42 +3793,42 @@
       </c>
       <c r="L19" s="80">
         <f t="shared" si="5"/>
-        <v>208649.14</v>
+        <v>145339.14000000001</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="6"/>
-        <v>221168.14</v>
+        <v>154059.14000000001</v>
       </c>
       <c r="N19" s="82">
         <f t="shared" si="7"/>
-        <v>214908.14</v>
+        <v>149699.14000000001</v>
       </c>
       <c r="O19" s="43">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="P19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="165">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="164">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="B20" s="165" t="s">
+      <c r="B20" s="164" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="166"/>
-      <c r="D20" s="167">
+      <c r="C20" s="165"/>
+      <c r="D20" s="166">
         <v>1.8</v>
       </c>
       <c r="E20" s="75">
-        <v>69487.149999999994</v>
+        <v>72884.149999999994</v>
       </c>
       <c r="F20" s="75">
         <f>E20</f>
-        <v>69487.149999999994</v>
+        <v>72884.149999999994</v>
       </c>
       <c r="G20" s="76">
         <f t="shared" si="1"/>
@@ -3944,7 +3843,7 @@
       </c>
       <c r="J20" s="78">
         <f t="shared" si="4"/>
-        <v>71333.687313000017</v>
+        <v>74900.371678650015</v>
       </c>
       <c r="K20" s="161">
         <f t="shared" si="2"/>
@@ -3952,25 +3851,25 @@
       </c>
       <c r="L20" s="80">
         <f t="shared" si="5"/>
-        <v>72884.149999999994</v>
+        <v>76451.149999999994</v>
       </c>
       <c r="M20" s="81">
         <f t="shared" si="6"/>
-        <v>77257.149999999994</v>
+        <v>81038.149999999994</v>
       </c>
       <c r="N20" s="82">
         <f t="shared" si="7"/>
-        <v>75071.149999999994</v>
+        <v>78745.149999999994</v>
       </c>
       <c r="O20" s="43">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
       <c r="P20" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -3983,11 +3882,11 @@
         <v>3.22</v>
       </c>
       <c r="E21" s="74">
-        <v>124305.16</v>
+        <v>130382.16</v>
       </c>
       <c r="F21" s="75">
         <f t="shared" si="10"/>
-        <v>124305.16</v>
+        <v>130382.16</v>
       </c>
       <c r="G21" s="76">
         <f t="shared" si="1"/>
@@ -4002,7 +3901,7 @@
       </c>
       <c r="J21" s="78">
         <f t="shared" si="4"/>
-        <v>127608.0406377</v>
+        <v>133988.442669585</v>
       </c>
       <c r="K21" s="161">
         <f t="shared" si="2"/>
@@ -4010,27 +3909,27 @@
       </c>
       <c r="L21" s="80">
         <f t="shared" si="5"/>
-        <v>130382.16</v>
+        <v>136762.16</v>
       </c>
       <c r="M21" s="81">
         <f t="shared" si="6"/>
-        <v>138205.16</v>
+        <v>144968.16</v>
       </c>
       <c r="N21" s="82">
         <f t="shared" si="7"/>
-        <v>134293.16</v>
+        <v>140865.16</v>
       </c>
       <c r="O21" s="43">
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
       <c r="P21" s="124"/>
-      <c r="Q21" s="169"/>
-      <c r="R21" s="169"/>
-      <c r="S21" s="169"/>
-      <c r="T21" s="169"/>
-    </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q21" s="168"/>
+      <c r="R21" s="168"/>
+      <c r="S21" s="168"/>
+      <c r="T21" s="168"/>
+    </row>
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="64">
         <f t="shared" si="8"/>
         <v>17</v>
@@ -4043,23 +3942,25 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="75">
-        <v>342737.17</v>
-      </c>
-      <c r="F22" s="75"/>
+        <v>472462.17</v>
+      </c>
+      <c r="F22" s="75">
+        <v>350000</v>
+      </c>
       <c r="G22" s="76">
         <f t="shared" si="1"/>
-        <v>342737.17</v>
+        <v>122462.16999999998</v>
       </c>
       <c r="H22" s="76">
         <f t="shared" si="3"/>
-        <v>10282.115099999999</v>
+        <v>3673.8650999999995</v>
       </c>
       <c r="I22" s="77">
         <v>0</v>
       </c>
       <c r="J22" s="78">
         <f t="shared" si="4"/>
-        <v>103433.84660384999</v>
+        <v>108605.5389340425</v>
       </c>
       <c r="K22" s="161">
         <f t="shared" si="2"/>
@@ -4067,29 +3968,29 @@
       </c>
       <c r="L22" s="80">
         <f t="shared" si="5"/>
-        <v>458701.17</v>
+        <v>236990.17</v>
       </c>
       <c r="M22" s="81">
         <f t="shared" si="6"/>
-        <v>486223.17</v>
+        <v>251210.17</v>
       </c>
       <c r="N22" s="82">
         <f t="shared" si="7"/>
-        <v>472462.17</v>
+        <v>244100.17</v>
       </c>
       <c r="O22" s="43">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
       <c r="P22" s="124" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q22" s="169"/>
-      <c r="R22" s="169"/>
-      <c r="S22" s="169"/>
-      <c r="T22" s="169"/>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="Q22" s="168"/>
+      <c r="R22" s="168"/>
+      <c r="S22" s="168"/>
+      <c r="T22" s="168"/>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="64">
         <f t="shared" si="8"/>
         <v>18</v>
@@ -4102,11 +4003,11 @@
         <v>4.28</v>
       </c>
       <c r="E23" s="74">
-        <v>165225.18</v>
+        <v>173302.18</v>
       </c>
       <c r="F23" s="75">
         <f t="shared" si="10"/>
-        <v>165225.18</v>
+        <v>173302.18</v>
       </c>
       <c r="G23" s="76">
         <f t="shared" si="1"/>
@@ -4121,7 +4022,7 @@
       </c>
       <c r="J23" s="78">
         <f t="shared" si="4"/>
-        <v>169615.65649980001</v>
+        <v>178096.43932479003</v>
       </c>
       <c r="K23" s="161">
         <f t="shared" si="2"/>
@@ -4129,33 +4030,33 @@
       </c>
       <c r="L23" s="80">
         <f t="shared" si="5"/>
-        <v>173302.18</v>
+        <v>181783.18</v>
       </c>
       <c r="M23" s="81">
         <f t="shared" si="6"/>
-        <v>183700.18</v>
+        <v>192690.18</v>
       </c>
       <c r="N23" s="82">
         <f t="shared" si="7"/>
-        <v>178501.18</v>
+        <v>187236.18</v>
       </c>
       <c r="O23" s="43">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="P23" s="169"/>
-      <c r="Q23" s="169"/>
-      <c r="R23" s="169"/>
-      <c r="S23" s="169"/>
-      <c r="T23" s="169"/>
-    </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="168"/>
+      <c r="Q23" s="168"/>
+      <c r="R23" s="168"/>
+      <c r="S23" s="168"/>
+      <c r="T23" s="168"/>
+    </row>
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="64"/>
       <c r="B24" s="64"/>
       <c r="C24" s="65"/>
       <c r="D24" s="73"/>
       <c r="E24" s="74"/>
-      <c r="F24" s="168"/>
+      <c r="F24" s="167"/>
       <c r="G24" s="76"/>
       <c r="H24" s="76"/>
       <c r="I24" s="77"/>
@@ -4169,7 +4070,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="83"/>
       <c r="B25" s="64"/>
       <c r="C25" s="65"/>
@@ -4186,7 +4087,7 @@
       <c r="N25" s="82"/>
       <c r="O25" s="43"/>
     </row>
-    <row r="26" spans="1:20" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="83"/>
       <c r="B26" s="66"/>
       <c r="C26" s="65"/>
@@ -4203,7 +4104,7 @@
       <c r="N26" s="82"/>
       <c r="O26" s="43"/>
     </row>
-    <row r="27" spans="1:20" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="84"/>
       <c r="B27" s="64"/>
       <c r="C27" s="65"/>
@@ -4220,7 +4121,7 @@
       <c r="N27" s="82"/>
       <c r="O27" s="43"/>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="64"/>
       <c r="B28" s="90"/>
       <c r="C28" s="90"/>
@@ -4237,7 +4138,7 @@
       <c r="N28" s="93"/>
       <c r="O28" s="43"/>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
       <c r="B29" s="95"/>
       <c r="C29" s="95"/>
@@ -4247,19 +4148,19 @@
       </c>
       <c r="E29" s="53">
         <f>SUM(E6:E28)</f>
-        <v>6392226.71</v>
+        <v>6137524.71</v>
       </c>
       <c r="F29" s="62">
         <f>SUM(F6:F28)</f>
-        <v>4401284.3499999996</v>
+        <v>3645653.3100000005</v>
       </c>
       <c r="G29" s="62">
         <f>SUM(G6:G28)</f>
-        <v>1990942.36</v>
+        <v>2491871.4</v>
       </c>
       <c r="H29" s="62">
         <f t="shared" ref="H29:M29" si="11">SUM(H6:H28)</f>
-        <v>67830.097800000003</v>
+        <v>78899.261699999988</v>
       </c>
       <c r="I29" s="62">
         <f t="shared" si="11"/>
@@ -4267,7 +4168,7 @@
       </c>
       <c r="J29" s="133">
         <f t="shared" si="11"/>
-        <v>3966153.0146027999</v>
+        <v>4164460.6653329404</v>
       </c>
       <c r="K29" s="62">
         <f t="shared" si="11"/>
@@ -4275,105 +4176,110 @@
       </c>
       <c r="L29" s="97">
         <f>SUM(L6:L23)</f>
-        <v>6111129.71</v>
+        <v>6821437.71</v>
       </c>
       <c r="M29" s="97">
         <f t="shared" si="11"/>
-        <v>6477797.71</v>
+        <v>7230726.71</v>
       </c>
       <c r="N29" s="97">
         <f>SUM(N6:N28)</f>
-        <v>6294463.71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7026079.71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="50"/>
       <c r="C30" s="50"/>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="190" t="str">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="193" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="190"/>
-      <c r="D32" s="190"/>
-      <c r="E32" s="190"/>
-      <c r="F32" s="190"/>
-      <c r="G32" s="190"/>
-      <c r="H32" s="190"/>
-      <c r="I32" s="190"/>
-      <c r="J32" s="190"/>
-      <c r="K32" s="190"/>
-      <c r="L32" s="190"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="190"/>
-      <c r="C33" s="190"/>
-      <c r="D33" s="190"/>
-      <c r="E33" s="190"/>
-      <c r="F33" s="190"/>
-      <c r="G33" s="190"/>
-      <c r="H33" s="190"/>
-      <c r="I33" s="190"/>
-      <c r="J33" s="190"/>
-      <c r="K33" s="190"/>
-      <c r="L33" s="190"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="190"/>
-      <c r="C34" s="190"/>
-      <c r="D34" s="190"/>
-      <c r="E34" s="190"/>
-      <c r="F34" s="190"/>
-      <c r="G34" s="190"/>
-      <c r="H34" s="190"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="190"/>
-      <c r="K34" s="190"/>
-      <c r="L34" s="190"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="190"/>
-      <c r="C35" s="190"/>
-      <c r="D35" s="190"/>
-      <c r="E35" s="190"/>
-      <c r="F35" s="190"/>
-      <c r="G35" s="190"/>
-      <c r="H35" s="190"/>
-      <c r="I35" s="190"/>
-      <c r="J35" s="190"/>
-      <c r="K35" s="190"/>
-      <c r="L35" s="190"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="190"/>
-      <c r="C36" s="190"/>
-      <c r="D36" s="190"/>
-      <c r="E36" s="190"/>
-      <c r="F36" s="190"/>
-      <c r="G36" s="190"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="190"/>
-      <c r="J36" s="190"/>
-      <c r="K36" s="190"/>
-      <c r="L36" s="190"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="190"/>
-      <c r="C37" s="190"/>
-      <c r="D37" s="190"/>
-      <c r="E37" s="190"/>
-      <c r="F37" s="190"/>
-      <c r="G37" s="190"/>
-      <c r="H37" s="190"/>
-      <c r="I37" s="190"/>
-      <c r="J37" s="190"/>
-      <c r="K37" s="190"/>
-      <c r="L37" s="190"/>
+      <c r="C32" s="193"/>
+      <c r="D32" s="193"/>
+      <c r="E32" s="193"/>
+      <c r="F32" s="193"/>
+      <c r="G32" s="193"/>
+      <c r="H32" s="193"/>
+      <c r="I32" s="193"/>
+      <c r="J32" s="193"/>
+      <c r="K32" s="193"/>
+      <c r="L32" s="193"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="193"/>
+      <c r="C33" s="193"/>
+      <c r="D33" s="193"/>
+      <c r="E33" s="193"/>
+      <c r="F33" s="193"/>
+      <c r="G33" s="193"/>
+      <c r="H33" s="193"/>
+      <c r="I33" s="193"/>
+      <c r="J33" s="193"/>
+      <c r="K33" s="193"/>
+      <c r="L33" s="193"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="193"/>
+      <c r="C34" s="193"/>
+      <c r="D34" s="193"/>
+      <c r="E34" s="193"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="193"/>
+      <c r="H34" s="193"/>
+      <c r="I34" s="193"/>
+      <c r="J34" s="193"/>
+      <c r="K34" s="193"/>
+      <c r="L34" s="193"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="193"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="193"/>
+      <c r="E35" s="193"/>
+      <c r="F35" s="193"/>
+      <c r="G35" s="193"/>
+      <c r="H35" s="193"/>
+      <c r="I35" s="193"/>
+      <c r="J35" s="193"/>
+      <c r="K35" s="193"/>
+      <c r="L35" s="193"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="193"/>
+      <c r="C36" s="193"/>
+      <c r="D36" s="193"/>
+      <c r="E36" s="193"/>
+      <c r="F36" s="193"/>
+      <c r="G36" s="193"/>
+      <c r="H36" s="193"/>
+      <c r="I36" s="193"/>
+      <c r="J36" s="193"/>
+      <c r="K36" s="193"/>
+      <c r="L36" s="193"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="193"/>
+      <c r="C37" s="193"/>
+      <c r="D37" s="193"/>
+      <c r="E37" s="193"/>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="193"/>
+      <c r="L37" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
@@ -4384,11 +4290,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4398,34 +4299,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A5:O10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="124"/>
       <c r="N5" s="124"/>
       <c r="O5" s="124"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="124"/>
       <c r="N6" s="124"/>
       <c r="O6" s="124"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="124"/>
       <c r="N7" s="124"/>
       <c r="O7" s="124"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="124"/>
       <c r="N8" s="124"/>
       <c r="O8" s="124"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="124"/>
       <c r="N9" s="124"/>
       <c r="O9" s="124"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="124"/>
       <c r="N10" s="124"/>
       <c r="O10" s="124"/>

--- a/2026/YRIGOYEN 7630/Mayo/YRIGOYEN7630-Mayo.xlsx
+++ b/2026/YRIGOYEN 7630/Mayo/YRIGOYEN7630-Mayo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD68E0C-4907-49B4-AE2D-201A2F5C1E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE066AB-9175-4F4C-9D06-B34B4603B513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="123">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -389,6 +389,18 @@
   </si>
   <si>
     <t>Transf 26/05</t>
+  </si>
+  <si>
+    <t>Anotacion:</t>
+  </si>
+  <si>
+    <t>Dpto</t>
+  </si>
+  <si>
+    <t>5 y 6</t>
+  </si>
+  <si>
+    <t>El mes pasado el 06 y el 05 pagaron impecable, pero le pusimos pago al 05 lo que iba en el 06 y pago al 06 lo que iba en el 05. El 06 debe abonar $200.896,06 y el 05 $341.480,05</t>
   </si>
 </sst>
 </file>
@@ -602,7 +614,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,6 +681,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1081,7 +1099,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1343,6 +1361,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="25" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1361,16 +1391,13 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1394,12 +1421,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1415,9 +1436,33 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1851,12 +1896,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="191" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="188"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="192"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -1894,49 +1939,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="190" t="s">
+      <c r="B8" s="194" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="190"/>
+      <c r="C8" s="194"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="190"/>
-      <c r="C9" s="190"/>
+      <c r="B9" s="194"/>
+      <c r="C9" s="194"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="190"/>
-      <c r="C10" s="190"/>
+      <c r="B10" s="194"/>
+      <c r="C10" s="194"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="189" t="s">
+      <c r="A13" s="193" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="189"/>
-      <c r="B14" s="189"/>
-      <c r="C14" s="189"/>
-      <c r="D14" s="189"/>
-      <c r="E14" s="189"/>
+      <c r="A14" s="193"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="189"/>
-      <c r="B15" s="189"/>
-      <c r="C15" s="189"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="189"/>
-      <c r="B16" s="189"/>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2067,10 +2112,10 @@
       <c r="E31" s="141"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="185" t="s">
+      <c r="A32" s="189" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="186"/>
+      <c r="B32" s="190"/>
       <c r="C32" s="52"/>
       <c r="D32" s="169">
         <v>45000</v>
@@ -2078,10 +2123,10 @@
       <c r="E32" s="142"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="185" t="s">
+      <c r="A33" s="189" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="186"/>
+      <c r="B33" s="190"/>
       <c r="C33" s="52"/>
       <c r="D33" s="175">
         <f>147300*2</f>
@@ -2114,10 +2159,10 @@
       <c r="E35" s="144"/>
     </row>
     <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="191" t="s">
+      <c r="A36" s="187" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="192"/>
+      <c r="B36" s="188"/>
       <c r="C36" s="54"/>
       <c r="D36" s="178">
         <f>26570+7909</f>
@@ -2128,10 +2173,10 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="185" t="s">
+      <c r="A37" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="186"/>
+      <c r="B37" s="190"/>
       <c r="C37" s="54"/>
       <c r="D37" s="179">
         <v>54278</v>
@@ -2315,10 +2360,10 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="191" t="s">
+      <c r="A51" s="187" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="192"/>
+      <c r="B51" s="188"/>
       <c r="C51" s="5"/>
       <c r="D51" s="157">
         <v>838862.61</v>
@@ -2375,10 +2420,10 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="191" t="s">
+      <c r="A56" s="187" t="s">
         <v>117</v>
       </c>
-      <c r="B56" s="192"/>
+      <c r="B56" s="188"/>
       <c r="C56" s="5"/>
       <c r="D56" s="106">
         <v>333100</v>
@@ -2388,10 +2433,10 @@
       </c>
     </row>
     <row r="57" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="191" t="s">
+      <c r="A57" s="187" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="192"/>
+      <c r="B57" s="188"/>
       <c r="C57" s="5"/>
       <c r="D57" s="106">
         <v>250000</v>
@@ -2401,10 +2446,10 @@
       </c>
     </row>
     <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="191" t="s">
+      <c r="A58" s="187" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="192"/>
+      <c r="B58" s="188"/>
       <c r="C58" s="5"/>
       <c r="D58" s="106">
         <v>78200</v>
@@ -2533,22 +2578,22 @@
       <c r="E70" s="118"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="191"/>
-      <c r="B71" s="192"/>
+      <c r="A71" s="187"/>
+      <c r="B71" s="188"/>
       <c r="C71" s="5"/>
       <c r="D71" s="128"/>
       <c r="E71" s="104"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="191"/>
-      <c r="B72" s="192"/>
+      <c r="A72" s="187"/>
+      <c r="B72" s="188"/>
       <c r="C72" s="5"/>
       <c r="D72" s="106"/>
       <c r="E72" s="104"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="185"/>
-      <c r="B73" s="186"/>
+      <c r="A73" s="189"/>
+      <c r="B73" s="190"/>
       <c r="C73" s="5"/>
       <c r="D73" s="106"/>
       <c r="E73" s="104"/>
@@ -2659,7 +2704,7 @@
       </c>
       <c r="B91" s="40">
         <f>PRORRATEO!F29</f>
-        <v>3645653.3100000005</v>
+        <v>3651399.3100000005</v>
       </c>
       <c r="C91" s="24"/>
     </row>
@@ -2718,7 +2763,7 @@
       </c>
       <c r="B98" s="59">
         <f>SUM(B90:B97)</f>
-        <v>-623257.74000000022</v>
+        <v>-617511.74000000022</v>
       </c>
       <c r="C98" s="27"/>
       <c r="D98" s="43"/>
@@ -2782,7 +2827,7 @@
       </c>
       <c r="B106" s="137">
         <f>PRORRATEO!F29</f>
-        <v>3645653.3100000005</v>
+        <v>3651399.3100000005</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2791,7 +2836,7 @@
       </c>
       <c r="B107" s="135">
         <f>SUM(B102:C106)</f>
-        <v>-1724274.5360999964</v>
+        <v>-1718528.5360999964</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,16 +2845,16 @@
     </row>
     <row r="109" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="194" t="s">
+      <c r="A110" s="186" t="s">
         <v>32</v>
       </c>
-      <c r="B110" s="194"/>
-      <c r="C110" s="194"/>
+      <c r="B110" s="186"/>
+      <c r="C110" s="186"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="194"/>
-      <c r="B111" s="194"/>
-      <c r="C111" s="194"/>
+      <c r="A111" s="186"/>
+      <c r="B111" s="186"/>
+      <c r="C111" s="186"/>
     </row>
     <row r="112" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="120"/>
@@ -2839,51 +2884,51 @@
       <c r="M115" s="8"/>
     </row>
     <row r="116" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="193"/>
-      <c r="B116" s="193"/>
-      <c r="C116" s="193"/>
-      <c r="D116" s="193"/>
-      <c r="E116" s="193"/>
+      <c r="A116" s="185"/>
+      <c r="B116" s="185"/>
+      <c r="C116" s="185"/>
+      <c r="D116" s="185"/>
+      <c r="E116" s="185"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="193"/>
-      <c r="B117" s="193"/>
-      <c r="C117" s="193"/>
-      <c r="D117" s="193"/>
-      <c r="E117" s="193"/>
+      <c r="A117" s="185"/>
+      <c r="B117" s="185"/>
+      <c r="C117" s="185"/>
+      <c r="D117" s="185"/>
+      <c r="E117" s="185"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="193"/>
-      <c r="B118" s="193"/>
-      <c r="C118" s="193"/>
-      <c r="D118" s="193"/>
-      <c r="E118" s="193"/>
+      <c r="A118" s="185"/>
+      <c r="B118" s="185"/>
+      <c r="C118" s="185"/>
+      <c r="D118" s="185"/>
+      <c r="E118" s="185"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="193"/>
-      <c r="B119" s="193"/>
-      <c r="C119" s="193"/>
-      <c r="D119" s="193"/>
-      <c r="E119" s="193"/>
+      <c r="A119" s="185"/>
+      <c r="B119" s="185"/>
+      <c r="C119" s="185"/>
+      <c r="D119" s="185"/>
+      <c r="E119" s="185"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A116:E119"/>
-    <mergeCell ref="A110:C111"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A116:E119"/>
+    <mergeCell ref="A110:C111"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2919,15 +2964,15 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
@@ -2974,46 +3019,46 @@
       <c r="N3" s="60"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="202" t="s">
+      <c r="A4" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="202" t="s">
+      <c r="C4" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="195" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="198" t="s">
+      <c r="E4" s="201" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="202" t="s">
+      <c r="F4" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="204" t="s">
+      <c r="G4" s="205" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="198" t="s">
+      <c r="H4" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="198" t="s">
+      <c r="I4" s="201" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="198" t="s">
+      <c r="J4" s="201" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="207" t="s">
+      <c r="K4" s="208" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="200" t="s">
+      <c r="M4" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="195" t="s">
+      <c r="N4" s="198" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="130">
@@ -3021,23 +3066,23 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="203"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="199"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="199"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="199"/>
-      <c r="K5" s="208"/>
+      <c r="A5" s="197"/>
+      <c r="B5" s="197"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="202"/>
+      <c r="F5" s="197"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="202"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="202"/>
+      <c r="K5" s="209"/>
       <c r="L5" s="61" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="M5" s="201"/>
-      <c r="N5" s="196"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="199"/>
     </row>
     <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="64">
@@ -3257,11 +3302,11 @@
       <c r="Q9" s="43"/>
     </row>
     <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="64">
+      <c r="A10" s="220">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="220" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="65"/>
@@ -3269,18 +3314,19 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="74">
-        <v>325601.05</v>
+        <v>335369.05</v>
       </c>
       <c r="F10" s="75">
-        <v>191523.06</v>
+        <f>E10</f>
+        <v>335369.05</v>
       </c>
       <c r="G10" s="76">
         <f t="shared" si="1"/>
-        <v>134077.99</v>
+        <v>0</v>
       </c>
       <c r="H10" s="76">
         <f t="shared" si="3"/>
-        <v>4022.3396999999995</v>
+        <v>0</v>
       </c>
       <c r="I10" s="77">
         <v>0</v>
@@ -3295,15 +3341,15 @@
       </c>
       <c r="L10" s="80">
         <f t="shared" si="5"/>
-        <v>479581.05</v>
+        <v>341480.05</v>
       </c>
       <c r="M10" s="81">
         <f t="shared" si="6"/>
-        <v>508356.05</v>
+        <v>361969.05</v>
       </c>
       <c r="N10" s="82">
         <f t="shared" si="7"/>
-        <v>493968.05</v>
+        <v>351724.05</v>
       </c>
       <c r="O10" s="43">
         <f t="shared" si="9"/>
@@ -3315,11 +3361,11 @@
       <c r="Q10" s="43"/>
     </row>
     <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="64">
+      <c r="A11" s="220">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="220" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="64"/>
@@ -3330,11 +3376,12 @@
         <v>197269.06</v>
       </c>
       <c r="F11" s="75">
-        <v>335369.05</v>
+        <f>E11</f>
+        <v>197269.06</v>
       </c>
       <c r="G11" s="76">
         <f t="shared" si="1"/>
-        <v>-138099.99</v>
+        <v>0</v>
       </c>
       <c r="H11" s="76">
         <f t="shared" si="3"/>
@@ -3353,15 +3400,15 @@
       </c>
       <c r="L11" s="80">
         <f t="shared" si="5"/>
-        <v>62796.06</v>
+        <v>200896.06</v>
       </c>
       <c r="M11" s="81">
         <f t="shared" si="6"/>
-        <v>66564.06</v>
+        <v>212950.06</v>
       </c>
       <c r="N11" s="82">
         <f t="shared" si="7"/>
-        <v>64680.06</v>
+        <v>206923.06</v>
       </c>
       <c r="O11" s="43">
         <f t="shared" si="9"/>
@@ -4148,19 +4195,19 @@
       </c>
       <c r="E29" s="53">
         <f>SUM(E6:E28)</f>
-        <v>6137524.71</v>
+        <v>6147292.71</v>
       </c>
       <c r="F29" s="62">
         <f>SUM(F6:F28)</f>
-        <v>3645653.3100000005</v>
+        <v>3651399.3100000005</v>
       </c>
       <c r="G29" s="62">
         <f>SUM(G6:G28)</f>
-        <v>2491871.4</v>
+        <v>2495893.4</v>
       </c>
       <c r="H29" s="62">
         <f t="shared" ref="H29:M29" si="11">SUM(H6:H28)</f>
-        <v>78899.261699999988</v>
+        <v>74876.922000000006</v>
       </c>
       <c r="I29" s="62">
         <f t="shared" si="11"/>
@@ -4176,15 +4223,15 @@
       </c>
       <c r="L29" s="97">
         <f>SUM(L6:L23)</f>
-        <v>6821437.71</v>
+        <v>6821436.71</v>
       </c>
       <c r="M29" s="97">
         <f t="shared" si="11"/>
-        <v>7230726.71</v>
+        <v>7230725.71</v>
       </c>
       <c r="N29" s="97">
         <f>SUM(N6:N28)</f>
-        <v>7026079.71</v>
+        <v>7026078.71</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4193,93 +4240,88 @@
     </row>
     <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="193" t="str">
+      <c r="B32" s="185" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="193"/>
-      <c r="D32" s="193"/>
-      <c r="E32" s="193"/>
-      <c r="F32" s="193"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="193"/>
-      <c r="I32" s="193"/>
-      <c r="J32" s="193"/>
-      <c r="K32" s="193"/>
-      <c r="L32" s="193"/>
+      <c r="C32" s="185"/>
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="185"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
     </row>
     <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="193"/>
-      <c r="C33" s="193"/>
-      <c r="D33" s="193"/>
-      <c r="E33" s="193"/>
-      <c r="F33" s="193"/>
-      <c r="G33" s="193"/>
-      <c r="H33" s="193"/>
-      <c r="I33" s="193"/>
-      <c r="J33" s="193"/>
-      <c r="K33" s="193"/>
-      <c r="L33" s="193"/>
+      <c r="B33" s="185"/>
+      <c r="C33" s="185"/>
+      <c r="D33" s="185"/>
+      <c r="E33" s="185"/>
+      <c r="F33" s="185"/>
+      <c r="G33" s="185"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="185"/>
+      <c r="K33" s="185"/>
+      <c r="L33" s="185"/>
     </row>
     <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="193"/>
-      <c r="C34" s="193"/>
-      <c r="D34" s="193"/>
-      <c r="E34" s="193"/>
-      <c r="F34" s="193"/>
-      <c r="G34" s="193"/>
-      <c r="H34" s="193"/>
-      <c r="I34" s="193"/>
-      <c r="J34" s="193"/>
-      <c r="K34" s="193"/>
-      <c r="L34" s="193"/>
+      <c r="B34" s="185"/>
+      <c r="C34" s="185"/>
+      <c r="D34" s="185"/>
+      <c r="E34" s="185"/>
+      <c r="F34" s="185"/>
+      <c r="G34" s="185"/>
+      <c r="H34" s="185"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="185"/>
+      <c r="K34" s="185"/>
+      <c r="L34" s="185"/>
     </row>
     <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="193"/>
-      <c r="C35" s="193"/>
-      <c r="D35" s="193"/>
-      <c r="E35" s="193"/>
-      <c r="F35" s="193"/>
-      <c r="G35" s="193"/>
-      <c r="H35" s="193"/>
-      <c r="I35" s="193"/>
-      <c r="J35" s="193"/>
-      <c r="K35" s="193"/>
-      <c r="L35" s="193"/>
+      <c r="B35" s="185"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="185"/>
+      <c r="E35" s="185"/>
+      <c r="F35" s="185"/>
+      <c r="G35" s="185"/>
+      <c r="H35" s="185"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="185"/>
+      <c r="K35" s="185"/>
+      <c r="L35" s="185"/>
     </row>
     <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="193"/>
-      <c r="C36" s="193"/>
-      <c r="D36" s="193"/>
-      <c r="E36" s="193"/>
-      <c r="F36" s="193"/>
-      <c r="G36" s="193"/>
-      <c r="H36" s="193"/>
-      <c r="I36" s="193"/>
-      <c r="J36" s="193"/>
-      <c r="K36" s="193"/>
-      <c r="L36" s="193"/>
+      <c r="B36" s="185"/>
+      <c r="C36" s="185"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="185"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="185"/>
     </row>
     <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="193"/>
-      <c r="C37" s="193"/>
-      <c r="D37" s="193"/>
-      <c r="E37" s="193"/>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="193"/>
-      <c r="L37" s="193"/>
+      <c r="B37" s="185"/>
+      <c r="C37" s="185"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="185"/>
+      <c r="F37" s="185"/>
+      <c r="G37" s="185"/>
+      <c r="H37" s="185"/>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="185"/>
+      <c r="L37" s="185"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
@@ -4290,6 +4332,11 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4298,26 +4345,75 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="A5:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="221" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="222">
+        <v>1</v>
+      </c>
+      <c r="D2" s="210"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="211"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="223" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="224" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="213"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="214" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="216"/>
+    </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
+      <c r="B5" s="214"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="216"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="124"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="216"/>
       <c r="N6" s="124"/>
       <c r="O6" s="124"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="124"/>
+      <c r="B7" s="214"/>
+      <c r="C7" s="215"/>
+      <c r="D7" s="215"/>
+      <c r="E7" s="215"/>
+      <c r="F7" s="216"/>
       <c r="N7" s="124"/>
       <c r="O7" s="124"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="124"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="219"/>
       <c r="N8" s="124"/>
       <c r="O8" s="124"/>
     </row>
@@ -4331,7 +4427,15 @@
       <c r="N10" s="124"/>
       <c r="O10" s="124"/>
     </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="124"/>
+      <c r="N11" s="124"/>
+      <c r="O11" s="124"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:F8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>